--- a/data/output/evaluasi_97.xlsx
+++ b/data/output/evaluasi_97.xlsx
@@ -9,13 +9,13 @@
   <sheets>
     <sheet name="9700" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="9701" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="9702" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="9703" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="9704" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="9705" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="9706" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9705" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9702" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9703" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9704" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9708" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="9707" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9708" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9706" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,20 +479,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6661220840556333</v>
+        <v>5.145619376227316</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4620271840518879</v>
+        <v>3.9687022553975</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -535,20 +535,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.582489861479378</v>
+        <v>0.1358548966864592</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -563,20 +563,692 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.039240373123912</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q2-25 vs q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
+        <v>-2.387991146024865</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.502963580774693</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.249723184844824</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-8.078107133982959</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.495039151494937</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.835963086287013</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.288278994382376</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-6.782395399551616</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.598267886314556</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.957651411258999</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.998129255719921</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-6.782395399551616</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.005439079919098951</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>97</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8149666850862556</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>97</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.07740999913212601</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>97</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.503013338032388</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>97</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4.484517647194348</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.566664002546303</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>97</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.01179573172193916</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>97</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>1.107406227485193</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7.076732677166209</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>97</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3.207114859683296</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>97</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.681927833583089</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.215417564205044</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -591,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,16 +1313,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1995.816633247118</v>
+        <v>1795.47448439188</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -665,20 +1337,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1225.83811819531</v>
+        <v>1845.01670078099</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -697,16 +1369,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.4792309313296704</v>
+        <v>1232.852595</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -721,20 +1393,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01603101248489476</v>
+        <v>1246.853210077203</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -753,16 +1425,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01603101248489476</v>
+        <v>0.4311252321481387</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>distribusi_net_ekspor_q1-25_ril vs distribusi_net_ekspor_q1-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -777,20 +1449,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5224995120572798</v>
+        <v>0.4356959962277649</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>distribusi_net_ekspor_q2-25_ril vs distribusi_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -805,20 +1477,328 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.243569607419489</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25_ril vs q-to-q_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.243569607419489</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_q_pdrb_q2-25_ril vs sog_q_pdrb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.006214224636353306</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.009010922223954458</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D11" t="n">
+        <v>3.704879527927463</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>59.77936594176989</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3349826587512835</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.750655372779379</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.479447658661523</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1716411097475623</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.012385329869325</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.6759671988873166</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-4.11920876822553</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -833,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,11 +1850,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9702</v>
+        <v>9705</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Jayawijaya</t>
+          <t>Kabupaten Mamberamo Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -883,72 +1863,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-7831.700639271882</v>
+        <v>3.195649388829269</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9702</v>
+        <v>9705</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Jayawijaya</t>
+          <t>Kabupaten Mamberamo Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-4624.796647790083</v>
+        <v>1.393669454016526</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9702</v>
+        <v>9705</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Jayawijaya</t>
+          <t>Kabupaten Mamberamo Tengah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1234599869998751</v>
+        <v>-0.5420439347678629</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.749544541810144</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -963,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,11 +2008,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lanny Jaya</t>
+          <t>Kabupaten Jayawijaya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1013,324 +2021,128 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2266.904137501106</v>
+        <v>5.985302804363776</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lanny Jaya</t>
+          <t>Kabupaten Jayawijaya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1174.41858665923</v>
+        <v>-1.418432323487541</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Lanny Jaya</t>
+          <t>Kabupaten Jayawijaya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.6737447783121397</v>
+        <v>8.563698317962292</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Lanny Jaya</t>
+          <t>Kabupaten Jayawijaya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4376690334147283</v>
+        <v>0.9479315624425272</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Lanny Jaya</t>
+          <t>Kabupaten Jayawijaya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.6737447783121397</v>
+        <v>0.2917475513444158</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.4376690334147283</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.3884103939706993</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1697526134727812</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2301412370030031</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.2306231759191915</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2220677840196069</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9703</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kabupaten Lanny Jaya</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.01083298460643426</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1345,7 +2157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,11 +2194,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9704</v>
+        <v>9703</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tolikara</t>
+          <t>Kabupaten Lanny Jaya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1395,156 +2207,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>130.5484296188747</v>
+        <v>2.645770066464249</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9704</v>
+        <v>9703</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tolikara</t>
+          <t>Kabupaten Lanny Jaya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>92.70360802876529</v>
+        <v>0.393900414439218</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9704</v>
+        <v>9703</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tolikara</t>
+          <t>Kabupaten Lanny Jaya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02336043185093399</v>
+        <v>0.5865757273984087</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9704</v>
+        <v>9703</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Tolikara</t>
+          <t>Kabupaten Lanny Jaya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02676879086243811</v>
+        <v>0.6641450530660268</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9704</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Tolikara</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1.263603955312377</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9704</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Tolikara</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2002311337283722</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1559,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,11 +2352,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9705</v>
+        <v>9704</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Mamberamo Tengah</t>
+          <t>Kabupaten Tolikara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1609,72 +2365,100 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1322.431817478606</v>
+        <v>2.297081895207046</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9705</v>
+        <v>9704</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Mamberamo Tengah</t>
+          <t>Kabupaten Tolikara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-678.4747255865175</v>
+        <v>0.4464432403230323</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9705</v>
+        <v>9704</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Mamberamo Tengah</t>
+          <t>Kabupaten Tolikara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.2627604472763059</v>
+        <v>0.1431077146107006</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.6605276654596741</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1689,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,11 +2510,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Yalimo</t>
+          <t>Kabupaten Pegunungan Bintang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1739,156 +2523,128 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>362.0490622435873</v>
+        <v>3.819202065010436</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Yalimo</t>
+          <t>Kabupaten Pegunungan Bintang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>235.1848331611287</v>
+        <v>-0.03134315136939974</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Yalimo</t>
+          <t>Kabupaten Pegunungan Bintang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01947991850293028</v>
+        <v>0.4359807425013514</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Yalimo</t>
+          <t>Kabupaten Pegunungan Bintang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01947991850293028</v>
+        <v>0.1932200458643847</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9706</v>
+        <v>9708</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Yalimo</t>
+          <t>Kabupaten Pegunungan Bintang</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4035162702127175</v>
+        <v>0.05255517245358941</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9706</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Yalimo</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.01070896676343281</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1903,7 +2659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,20 +2705,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3900.940076887241</v>
+        <v>0.2448810790060571</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1977,20 +2733,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2061.70567633996</v>
+        <v>0.1879887047246289</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2005,20 +2761,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1198833047341119</v>
+        <v>1.099297335765873</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2033,48 +2789,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.3989261303273925</v>
+        <v>0.5017726515947467</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9707</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Yahukimo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.242547797323454</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2126,309 +2854,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9708</v>
+        <v>9706</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pegunungan Bintang</t>
+          <t>Kabupaten Yalimo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1449.406157818247</v>
+        <v>0.08295270773025072</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9708</v>
+        <v>9706</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pegunungan Bintang</t>
+          <t>Kabupaten Yalimo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-851.1607085087456</v>
+        <v>-0.4775200777707608</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.6153416441202593</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.05698577450050816</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.6153416441202593</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.05698577450050816</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.04527534277049178</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.02537367257840328</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.08322279598872453</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.1741483822799557</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9708</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kabupaten Pegunungan Bintang</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.02236521360359226</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_97.xlsx
+++ b/data/output/evaluasi_97.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
